--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI18"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,245 +498,175 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Cantos_H</t>
+          <t>status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Cantos_A</t>
+          <t>Odd_H_FT</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Odd_D_FT</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_FT</t>
+          <t>Odd_A_FT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_FT</t>
+          <t>Odd_H_HT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_FT</t>
+          <t>Odd_D_HT</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Under25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under45</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>MinGolsH</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>MinGolsA</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_A</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_D</t>
+          <t>ChutegolH</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_D</t>
+          <t>ChutegolA</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_A</t>
+          <t>ChuteTotalH</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_75</t>
+          <t>ChuteTotalA</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_85</t>
+          <t>XGHome</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_95</t>
+          <t>XGAway</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_105</t>
+          <t>AtaquePerigosoH</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_115</t>
+          <t>AtaquePerigosoA</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_75</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_85</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_95</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_105</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_115</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_1</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_2</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_over05</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_over15</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under05</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under15</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under25</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -789,25 +719,25 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>-1</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>3.14</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>3.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -854,11 +784,15 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -870,16 +804,16 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -893,49 +827,7 @@
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46168.5</v>
       </c>
     </row>
@@ -960,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -986,16 +878,16 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>-1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -1051,11 +943,15 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1067,16 +963,16 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1090,49 +986,7 @@
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="3" t="n">
+      <c r="AU3" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -1157,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1183,16 +1037,16 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>-1</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1248,11 +1102,15 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1264,16 +1122,16 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1287,49 +1145,7 @@
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="3" t="n">
+      <c r="AU4" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -1380,16 +1196,16 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>-1</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1445,11 +1261,15 @@
       <c r="AG5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -1461,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1484,49 +1304,7 @@
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="3" t="n">
+      <c r="AU5" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -1551,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1577,16 +1355,16 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>-1</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1642,11 +1420,15 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -1658,16 +1440,16 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1681,49 +1463,7 @@
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="3" t="n">
+      <c r="AU6" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -1748,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1774,16 +1514,16 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>-1</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1839,11 +1579,15 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -1855,16 +1599,16 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1878,49 +1622,7 @@
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="3" t="n">
+      <c r="AU7" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -1971,25 +1673,25 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>-1</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>3.15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2036,11 +1738,15 @@
       <c r="AG8" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -2052,16 +1758,16 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2075,49 +1781,7 @@
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="3" t="n">
+      <c r="AU8" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -2142,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2168,16 +1832,16 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-1</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2233,11 +1897,15 @@
       <c r="AG9" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -2249,16 +1917,16 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -2272,49 +1940,7 @@
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="3" t="n">
+      <c r="AU9" s="3" t="n">
         <v>46168.54166666666</v>
       </c>
     </row>
@@ -2339,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2365,16 +1991,16 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
-        <v>-1</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2430,11 +2056,15 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -2446,16 +2076,16 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -2469,49 +2099,7 @@
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="3" t="n">
+      <c r="AU10" s="3" t="n">
         <v>46168.58333333334</v>
       </c>
     </row>
@@ -2536,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2562,16 +2150,16 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>-1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -2627,11 +2215,15 @@
       <c r="AG11" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2643,16 +2235,16 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2666,49 +2258,7 @@
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="3" t="n">
+      <c r="AU11" s="3" t="n">
         <v>46168.58333333334</v>
       </c>
     </row>
@@ -2733,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2759,16 +2309,16 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>-1</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2824,11 +2374,15 @@
       <c r="AG12" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2840,16 +2394,16 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2863,49 +2417,7 @@
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="3" t="n">
+      <c r="AU12" s="3" t="n">
         <v>46168.58333333334</v>
       </c>
     </row>
@@ -2920,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2956,19 +2468,19 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
-        <v>-1</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>2.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3001,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -3021,11 +2533,15 @@
       <c r="AG13" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -3037,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -3060,49 +2576,7 @@
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="3" t="n">
+      <c r="AU13" s="3" t="n">
         <v>46168.58333333334</v>
       </c>
     </row>
@@ -3117,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3153,25 +2627,25 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
-        <v>-1</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,19 +2684,23 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -3234,16 +2712,16 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3257,49 +2735,7 @@
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="3" t="n">
+      <c r="AU14" s="3" t="n">
         <v>46168.58333333334</v>
       </c>
     </row>
@@ -3324,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3350,16 +2786,16 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>-1</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -3415,11 +2851,15 @@
       <c r="AG15" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -3431,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3454,49 +2894,7 @@
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI15" s="3" t="n">
+      <c r="AU15" s="3" t="n">
         <v>46168.58333333334</v>
       </c>
     </row>
@@ -3547,16 +2945,16 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="n">
-        <v>-1</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -3612,11 +3010,15 @@
       <c r="AG16" t="n">
         <v>0</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -3628,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -3651,49 +3053,7 @@
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="3" t="n">
+      <c r="AU16" s="3" t="n">
         <v>46168.66666666666</v>
       </c>
     </row>
@@ -3718,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3744,16 +3104,16 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>-1</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -3809,11 +3169,15 @@
       <c r="AG17" t="n">
         <v>0</v>
       </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -3825,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -3848,49 +3212,7 @@
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" s="3" t="n">
+      <c r="AU17" s="3" t="n">
         <v>46168.67708333334</v>
       </c>
     </row>
@@ -3915,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3941,16 +3263,16 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>-1</v>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4006,11 +3328,15 @@
       <c r="AG18" t="n">
         <v>0</v>
       </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -4022,16 +3348,16 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -4045,49 +3371,7 @@
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="3" t="n">
+      <c r="AU18" s="3" t="n">
         <v>46168.67708333334</v>
       </c>
     </row>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -734,10 +734,10 @@
         <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.51</v>
+        <v>4.83</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>4.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.83</v>
+        <v>1.51</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.53</v>
+        <v>4.48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.83</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>4.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.51</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>4.48</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>5.45</v>
+        <v>4.55</v>
       </c>
       <c r="P17" t="n">
-        <v>4.85</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>5.65</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="V17" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.27</v>
+        <v>2.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.61</v>
+        <v>1.14</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>1.41</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>5.45</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>4.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Z18" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.77</v>
+        <v>3.27</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.14</v>
+        <v>2.61</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>4.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="T17" t="n">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.14</v>
+        <v>4.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.14</v>
+        <v>2.63</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>5.45</v>
+        <v>4.65</v>
       </c>
       <c r="P18" t="n">
-        <v>4.85</v>
+        <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="T18" t="n">
-        <v>5.65</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.61</v>
+        <v>1.17</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="P17" t="n">
-        <v>4.3</v>
+        <v>1.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="T17" t="n">
-        <v>5.65</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="V17" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.63</v>
+        <v>1.17</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.51</v>
+        <v>4.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="S18" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.17</v>
+        <v>2.63</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.51</v>
+        <v>4.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="S17" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="T17" t="n">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="U17" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.17</v>
+        <v>2.63</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="P18" t="n">
-        <v>4.3</v>
+        <v>1.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="T18" t="n">
-        <v>5.65</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.63</v>
+        <v>1.17</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3110,22 +3110,22 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q17" t="n">
         <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="T17" t="n">
         <v>5.65</v>
@@ -3143,22 +3143,22 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z17" t="n">
         <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE17" t="n">
         <v>1.67</v>
@@ -3183,7 +3183,7 @@
         <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,25 +3269,25 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="S18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
         <v>1.88</v>
@@ -3311,10 +3311,10 @@
         <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
         <v>1.95</v>
@@ -3323,10 +3323,10 @@
         <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2795,10 +2795,10 @@
         <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q15" t="n">
         <v>2.7</v>
@@ -2813,7 +2813,7 @@
         <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
         <v>1.42</v>
@@ -2822,22 +2822,22 @@
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
         <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
         <v>1.33</v>
@@ -2846,10 +2846,10 @@
         <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46168.58333333334</v>
+        <v>46168.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46168.58333333334</v>
+        <v>46168.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46168.66666666666</v>
+        <v>46168.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3063,27 +3063,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46168.67708333334</v>
+        <v>46168.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -3222,156 +3222,633 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Zrinjski</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Velež</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>46168.58333333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Spain Primera Division Women</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Atletico Madrid W</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tenerife W</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="3" t="n">
+        <v>46168.66666666666</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Stjarnan</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Víkingur Reykjavík</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.9</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R20" t="n">
         <v>2.52</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S20" t="n">
         <v>1.14</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="U20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y20" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Z20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.9</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.86</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AE20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK20" t="n">
         <v>1.17</v>
       </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="3" t="n">
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>46168.67708333334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n">
         <v>46168.67708333334</v>
       </c>
     </row>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,16 +1847,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK2" t="n">
         <v>1.26</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,16 +1847,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.85</v>
+        <v>1.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.14</v>
       </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AB20" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4.2</v>
-      </c>
       <c r="Q21" t="n">
-        <v>1.92</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="S21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T21" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.45</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
         <v>1.26</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>3.05</v>
+        <v>5.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.5</v>
       </c>
-      <c r="O20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4.2</v>
-      </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="S20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.31</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AB20" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.85</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>1.93</v>
       </c>
       <c r="R21" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.14</v>
       </c>
-      <c r="T21" t="n">
-        <v>5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AB21" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
         <v>3.4</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1370,16 +1370,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.85</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Q20" t="n">
         <v>3.9</v>
@@ -3620,13 +3620,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
         <v>2.9</v>
@@ -3638,7 +3638,7 @@
         <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
         <v>1.42</v>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O21" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="P21" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
         <v>3</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>1.51</v>
       </c>
       <c r="O20" t="n">
-        <v>4.55</v>
+        <v>4.95</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.17</v>
       </c>
-      <c r="T20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.51</v>
+        <v>4.15</v>
       </c>
       <c r="O21" t="n">
-        <v>4.95</v>
+        <v>4.55</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="S21" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.45</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
         <v>3.4</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1370,16 +1370,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
         <v>3.45</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.51</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.95</v>
+        <v>4.55</v>
       </c>
       <c r="P20" t="n">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="S20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.15</v>
+        <v>1.51</v>
       </c>
       <c r="O21" t="n">
-        <v>4.55</v>
+        <v>4.95</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.17</v>
       </c>
-      <c r="T21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,16 +1847,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>1.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.55</v>
+        <v>5.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>4.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.17</v>
       </c>
-      <c r="T20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.51</v>
+        <v>4.82</v>
       </c>
       <c r="O21" t="n">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="S21" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.31</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.45</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,16 +1847,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
       <c r="O16" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.65</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.5</v>
+        <v>4.82</v>
       </c>
       <c r="O20" t="n">
-        <v>5.1</v>
+        <v>4.45</v>
       </c>
       <c r="P20" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="S20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.31</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AB20" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.82</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.17</v>
       </c>
-      <c r="T21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.17</v>
+        <v>2.45</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -740,19 +740,19 @@
         <v>2.38</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -761,28 +761,28 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.46</v>
+        <v>2.69</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,25 +2156,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.33</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7</v>
+        <v>2.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,25 +3269,25 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3590,16 +3590,16 @@
         <v>4.82</v>
       </c>
       <c r="O20" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
         <v>1.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="S20" t="n">
         <v>1.17</v>
@@ -3626,19 +3626,19 @@
         <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AB20" t="n">
         <v>2.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
         <v>1.42</v>
@@ -3660,7 +3660,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="P21" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Q21" t="n">
         <v>1.83</v>
@@ -3761,16 +3761,16 @@
         <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="T21" t="n">
         <v>5.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="W21" t="n">
         <v>1.31</v>
@@ -3779,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z21" t="n">
         <v>10</v>
@@ -3788,10 +3788,10 @@
         <v>1.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AD21" t="n">
         <v>2.4</v>
@@ -3819,7 +3819,7 @@
         <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="O6" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>4.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>2.43</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.15</v>
       </c>
-      <c r="AF7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.54</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="P11" t="n">
-        <v>4.24</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.43</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q13" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.57</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AG13" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="P14" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.63</v>
+        <v>6.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.83</v>
+        <v>4.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.61</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="S15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.3</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3272,10 +3272,10 @@
         <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>5.7</v>
+        <v>5.63</v>
       </c>
       <c r="Q18" t="n">
         <v>2.04</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>14.5</v>
+        <v>3.82</v>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>4.27</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.65</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>3.76</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
         <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.88</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.76</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
         <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.24</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z14" t="n">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="P15" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>6.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>4.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.39</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.33</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.05</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.33</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.42</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.82</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB20" t="n">
         <v>4.4</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="AC20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.17</v>
       </c>
-      <c r="T20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.54</v>
+        <v>4.82</v>
       </c>
       <c r="O21" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="S21" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.38</v>
+        <v>1.15</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>4.24</v>
+        <v>4.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.15</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.65</v>
+        <v>6.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.82</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.27</v>
+        <v>1.37</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>1.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.6</v>
+        <v>1.02</v>
       </c>
       <c r="O8" t="n">
-        <v>4.55</v>
+        <v>14.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.37</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.37</v>
+        <v>4.33</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>14.5</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>4.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.61</v>
+        <v>3.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R12" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.3</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.84</v>
+        <v>6.24</v>
       </c>
       <c r="R13" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>2.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.24</v>
+        <v>4.39</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.45</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.63</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U16" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.3</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,52 +3110,52 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>5.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.39</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S17" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T17" t="n">
         <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
         <v>1.23</v>
@@ -3164,10 +3164,10 @@
         <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.22</v>
+        <v>2.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>5.63</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>4.38</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
         <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.54</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="P3" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>20.04</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.37</v>
+        <v>4.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.15</v>
       </c>
-      <c r="O7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.8</v>
+        <v>1.29</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="P9" t="n">
-        <v>4.27</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>4.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.24</v>
+        <v>1.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
         <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="P12" t="n">
-        <v>3.15</v>
+        <v>2.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.24</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="S13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.88</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.76</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
         <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.39</v>
+        <v>6.24</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.22</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>3.76</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
         <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>4.39</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.33</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.42</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.85</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="S20" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>5.55</v>
+        <v>3.84</v>
       </c>
       <c r="U20" t="n">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="V20" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.38</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.82</v>
+        <v>1.54</v>
       </c>
       <c r="O21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB21" t="n">
         <v>4.4</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="AC21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.17</v>
       </c>
-      <c r="T21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>20.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.73</v>
+        <v>1.09</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>20.04</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.65</v>
       </c>
-      <c r="AA6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="O7" t="n">
         <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>3.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>3.07</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.29</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.71</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>4.76</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
@@ -2348,31 +2348,31 @@
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC12" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG12" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.3</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R14" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
         <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,16 +2792,16 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="O15" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.24</v>
+        <v>6.03</v>
       </c>
       <c r="R15" t="n">
         <v>2.5</v>
@@ -2813,28 +2813,28 @@
         <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="V15" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
         <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
         <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC15" t="n">
         <v>2.55</v>
@@ -2843,7 +2843,7 @@
         <v>1.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
         <v>1.73</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="P16" t="n">
-        <v>2.61</v>
+        <v>6.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.47</v>
+        <v>2.29</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="P17" t="n">
-        <v>5.63</v>
+        <v>2.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.39</v>
+        <v>2.72</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
         <v>1.04</v>
@@ -3302,31 +3302,31 @@
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3381,27 +3381,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3424,68 +3424,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>5.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P19" t="n">
-        <v>4.15</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>3.88</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="V19" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46168.66666666666</v>
+        <v>46168.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>1.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>2.21</v>
       </c>
       <c r="R20" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.84</v>
+        <v>3.12</v>
       </c>
       <c r="U20" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>3.96</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.14</v>
+        <v>2.01</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46168.67708333334</v>
+        <v>46168.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3714,141 +3714,300 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>46168.67708333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Valur</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>1.54</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>5.2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>4.45</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>1.83</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>3</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>1.09</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>5.6</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>1.66</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V22" t="n">
         <v>2.12</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W22" t="n">
         <v>1.33</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.05</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z22" t="n">
         <v>10</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AA22" t="n">
         <v>1.14</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AB22" t="n">
         <v>4.4</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC22" t="n">
         <v>1.46</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AD22" t="n">
         <v>2.4</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AF22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AG22" t="n">
         <v>3.4</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.17</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AK22" t="n">
         <v>2.38</v>
       </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" s="3" t="n">
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="3" t="n">
         <v>46168.67708333334</v>
       </c>
     </row>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,55 +725,55 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>1.13</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="P3" t="n">
-        <v>20.04</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>3.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>3.07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.82</v>
+        <v>6.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P7" t="n">
-        <v>3.78</v>
+        <v>1.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="O9" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>8.5</v>
+        <v>20.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.87</v>
+        <v>4.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.73</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>2.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.76</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
         <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.87</v>
+        <v>1.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>6.03</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.86</v>
+        <v>4.76</v>
       </c>
       <c r="R14" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.75</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.03</v>
+        <v>2.72</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>2.29</v>
+        <v>3.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.94</v>
+        <v>3.11</v>
       </c>
       <c r="P16" t="n">
-        <v>6.06</v>
+        <v>2.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.58</v>
+        <v>3.02</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="O17" t="n">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="P17" t="n">
-        <v>2.71</v>
+        <v>6.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="U17" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.05</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="R18" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.45</v>
+        <v>2.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="O3" t="n">
-        <v>6.2</v>
+        <v>4.55</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>1.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="P4" t="n">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.58</v>
+        <v>1.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.96</v>
+        <v>17</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>20.04</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.35</v>
+        <v>4.33</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.6</v>
+        <v>1.09</v>
       </c>
       <c r="O7" t="n">
-        <v>4.55</v>
+        <v>6.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.31</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>8.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.36</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.18</v>
+        <v>1.29</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.03</v>
       </c>
-      <c r="O9" t="n">
-        <v>17</v>
-      </c>
-      <c r="P9" t="n">
-        <v>20.04</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.33</v>
+        <v>1.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>3.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>4.76</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
         <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.03</v>
+        <v>2.86</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="S13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.25</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.76</v>
+        <v>6.03</v>
       </c>
       <c r="R14" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
         <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>2.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.94</v>
+        <v>3.11</v>
       </c>
       <c r="P17" t="n">
-        <v>6.06</v>
+        <v>2.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.04</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.58</v>
+        <v>3.02</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>6.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.86</v>
+        <v>2.11</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="U18" t="n">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.48</v>
+        <v>2.29</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.88</v>
       </c>
-      <c r="U2" t="n">
-        <v>2.63</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.96</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
-        <v>20.04</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.33</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="O7" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>20.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.78</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.07</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
         <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>3.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="R13" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="S13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.3</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.45</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.44</v>
+        <v>2.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.03</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.06</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="P15" t="n">
-        <v>2.87</v>
+        <v>6.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.06</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="R16" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>3.04</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.45</v>
+        <v>2.69</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.39</v>
+        <v>5.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>6.06</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.11</v>
+        <v>6.03</v>
       </c>
       <c r="R18" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>2.96</v>
+        <v>2.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.29</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,34 +3428,34 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.25</v>
+        <v>5.18</v>
       </c>
       <c r="O19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.75</v>
+        <v>5.23</v>
       </c>
       <c r="R19" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U19" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
@@ -3467,25 +3467,25 @@
         <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
         <v>2.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD19" t="n">
         <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF19" t="n">
         <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3749,10 +3749,10 @@
         <v>4.15</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="Q21" t="n">
         <v>4.8</v>
@@ -3761,65 +3761,65 @@
         <v>2.63</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T21" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="V21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,31 +3905,31 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="P22" t="n">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="S22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T22" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="W22" t="n">
         <v>1.33</v>
@@ -3938,31 +3938,31 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
         <v>1.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -717,11 +717,11 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46168.5</v>
@@ -852,16 +852,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -873,118 +873,118 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.55</v>
+        <v>6.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>['47', '52', '87', '90+5']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1001,32 +1001,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1039,111 +1039,111 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.78</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>5.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>2.07</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.08</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1170,45 +1170,45 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>7.12</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '82']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '57', '66']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1319,29 +1319,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1350,118 +1350,118 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85', '86']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '77', '82']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1488,45 +1488,45 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>3.92</v>
       </c>
       <c r="P7" t="n">
-        <v>20.04</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.33</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '59', '66']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '79']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1647,45 +1647,45 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="O8" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1740,14 +1740,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>['25', '48', '90']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,19 +1806,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1830,115 +1830,115 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>6.2</v>
+        <v>3.44</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.1</v>
       </c>
-      <c r="AK9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1965,45 +1965,45 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>29</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.07</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '12', '18', '20', '43', '59', '90+5']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46168.54166666666</v>
@@ -2124,16 +2124,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -2145,118 +2145,118 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>3.78</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['82', '89']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46168.54166666666</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2311,56 +2311,56 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>1.97</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.76</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
         <v>1.24</v>
@@ -2369,10 +2369,10 @@
         <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,37 +2385,37 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="S13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="U13" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>4.66</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
         <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,19 +2760,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2784,72 +2784,72 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.39</v>
+        <v>4.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>6.06</v>
+        <v>1.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.11</v>
+        <v>5.21</v>
       </c>
       <c r="R15" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="T15" t="n">
-        <v>2.59</v>
+        <v>3.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.96</v>
+        <v>2.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.06</v>
+        <v>1.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>2.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.11</v>
+        <v>1.47</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2858,41 +2858,41 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '53', '55', '84']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.29</v>
+        <v>1.08</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.4</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AD16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="U17" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
         <v>2.15</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,149 +3227,149 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.03</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '41']</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46168.58333333334</v>
@@ -3596,71 +3596,71 @@
         <v>4.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK20" t="n">
         <v>2.23</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.01</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.15</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="S21" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T21" t="n">
-        <v>3.96</v>
+        <v>5.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.03</v>
+        <v>1.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.13</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,65 +3905,65 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>4.15</v>
       </c>
       <c r="O22" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>1.41</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>4.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="S22" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="T22" t="n">
-        <v>5.75</v>
+        <v>3.96</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="W22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.33</v>
       </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AB22" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.43</v>
+        <v>2.03</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG22" t="n">
         <v>2.5</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,139 +852,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['85', '86']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>['59', '77', '82']</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AN3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AR3" t="n">
         <v>1.98</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>['47', '52', '87', '90+5']</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
       <c r="AS3" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="AT3" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="P4" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.07</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['15', '59', '66']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['45+1', '79']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN4" t="n">
         <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.63</v>
+        <v>1.16</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,139 +1170,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="O5" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['43', '82']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['41', '57', '66']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>4</v>
       </c>
-      <c r="AN5" t="n">
-        <v>10</v>
-      </c>
       <c r="AO5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.99</v>
+        <v>1.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.31</v>
+        <v>1.61</v>
       </c>
       <c r="AS5" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="AT5" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1329,139 +1329,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>['85', '86']</t>
+          <t>['47', '52', '87', '90+5']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['59', '77', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.98</v>
+        <v>1.91</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="AT6" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1488,25 +1488,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>3.92</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>4.5</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['15', '59', '66']</t>
+          <t>['4', '12', '18', '20', '43', '59', '90+5']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['45+1', '79']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" t="n">
         <v>4</v>
       </c>
-      <c r="AN7" t="n">
-        <v>3</v>
-      </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.16</v>
+        <v>0.66</v>
       </c>
       <c r="AS7" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AT7" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1796,29 +1796,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1827,10 +1827,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.44</v>
+        <v>5.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['82', '89']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
         <v>4</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>2</v>
       </c>
-      <c r="AN9" t="n">
-        <v>4</v>
-      </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.61</v>
+        <v>0.59</v>
       </c>
       <c r="AS9" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="AT9" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1955,122 +1955,122 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O10" t="n">
-        <v>19</v>
-      </c>
-      <c r="P10" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AB10" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['4', '12', '18', '20', '43', '59', '90+5']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2079,22 +2079,22 @@
         <v>2</v>
       </c>
       <c r="AN10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="AS10" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>16</v>
@@ -2114,122 +2114,122 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>7.12</v>
       </c>
       <c r="O11" t="n">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['82', '89']</t>
+          <t>['43', '82']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '57', '66']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2238,25 +2238,25 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP11" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.59</v>
+        <v>2.31</v>
       </c>
       <c r="AS11" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="AT11" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46168.54166666666</v>
@@ -2283,31 +2283,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>4.66</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.37</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AE12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>['14', '52']</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>3</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>4</v>
       </c>
-      <c r="AN12" t="n">
-        <v>3</v>
-      </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.88</v>
+        <v>1.59</v>
       </c>
       <c r="AS12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="AT12" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,68 +2470,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T13" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,37 +2544,37 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2601,139 +2601,139 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.66</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="U14" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
         <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '90+5']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '61']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,139 +2919,139 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '43', '48']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '64', '73', '85']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46168.58333333334</v>
@@ -3068,149 +3068,149 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
         <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T17" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '41']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46168.58333333334</v>
@@ -3227,35 +3227,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.15</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.04</v>
       </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>['15', '45+5', '82']</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>['19', '41']</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK18" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3351,25 +3351,25 @@
         <v>5</v>
       </c>
       <c r="AN18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.26</v>
+        <v>0.65</v>
       </c>
       <c r="AS18" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="AT18" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46168.58333333334</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3564,26 +3564,26 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+8', '48']</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '90+2']</t>
         </is>
       </c>
       <c r="AJ20" t="n">
@@ -3666,28 +3666,28 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU20" s="3" t="n">
         <v>46168.66666666666</v>
@@ -3723,57 +3723,57 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="Q21" t="n">
         <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="S21" t="n">
         <v>1.08</v>
       </c>
       <c r="T21" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
         <v>2.17</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3788,10 +3788,10 @@
         <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD21" t="n">
         <v>2.5</v>
@@ -3800,53 +3800,53 @@
         <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '9', '65']</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN21" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP21" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46168.67708333334</v>
@@ -3882,54 +3882,54 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.15</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.8</v>
+        <v>5.96</v>
       </c>
       <c r="R22" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S22" t="n">
         <v>1.18</v>
       </c>
       <c r="T22" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W22" t="n">
         <v>1.18</v>
@@ -3938,74 +3938,74 @@
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
         <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '36', '65']</t>
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO22" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU22" s="3" t="n">
         <v>46168.67708333334</v>

--- a/jogos_2026-05-26.xlsx
+++ b/jogos_2026-05-26.xlsx
@@ -852,22 +852,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['85', '86']</t>
+          <t>['25', '48', '90']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>['59', '77', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -966,25 +966,25 @@
         <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="AT3" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>3.92</v>
+        <v>19</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.07</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['15', '59', '66']</t>
+          <t>['4', '12', '18', '20', '43', '59', '90+5']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['45+1', '79']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="n">
         <v>4</v>
       </c>
-      <c r="AN4" t="n">
-        <v>3</v>
-      </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.16</v>
+        <v>0.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AT4" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,28 +1170,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>4.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['15', '59', '66']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['45+1', '79']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>4</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2</v>
-      </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="AS5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AT5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1329,139 +1329,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['43', '82']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['41', '57', '66']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="AN6" t="n">
         <v>10</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>['47', '52', '87', '90+5']</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.91</v>
+        <v>0.99</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="AS6" t="n">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="AT6" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,28 +1488,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.01</v>
       </c>
-      <c r="O7" t="n">
-        <v>19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['4', '12', '18', '20', '43', '59', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1605,22 +1605,22 @@
         <v>4</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.66</v>
+        <v>1.61</v>
       </c>
       <c r="AS7" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="S8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['47', '52', '87', '90+5']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['25', '48', '90']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>7</v>
-      </c>
       <c r="AO8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.99</v>
+        <v>1.91</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="AT8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1806,139 +1806,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>['82', '89']</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>4</v>
-      </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP9" t="n">
         <v>7</v>
       </c>
-      <c r="AP9" t="n">
-        <v>3</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>1.28</v>
+        <v>0.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="AS9" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46168.54166666666</v>
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AE10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['82', '89']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP10" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>0.7</v>
+        <v>1.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="AT10" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46168.54166666666</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2139,16 +2139,16 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.12</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>5.05</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['43', '82']</t>
+          <t>['85', '86']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>['41', '57', '66']</t>
+          <t>['59', '77', '82']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
@@ -2238,25 +2238,25 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
         <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.31</v>
+        <v>1.98</v>
       </c>
       <c r="AS11" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AT11" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46168.54166666666</v>
@@ -2283,31 +2283,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>1.97</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.66</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2381,41 +2381,41 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>['14', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN12" t="n">
         <v>3</v>
       </c>
-      <c r="AN12" t="n">
-        <v>4</v>
-      </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.59</v>
+        <v>0.88</v>
       </c>
       <c r="AS12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AT12" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,28 +2442,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V13" t="n">
         <v>1.34</v>
@@ -2507,74 +2507,74 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>['15', '45+5', '82']</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP13" t="n">
         <v>3</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="AS13" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AT13" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2601,16 +2601,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2622,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>4.66</v>
       </c>
       <c r="R14" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
         <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>['55', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>['19', '61']</t>
+          <t>['14', '52']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.07</v>
+        <v>1.59</v>
       </c>
       <c r="AS14" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="AT14" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2760,31 +2760,31 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2792,107 +2792,107 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.15</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>3.13</v>
       </c>
       <c r="P15" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.21</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="S15" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>2.68</v>
       </c>
       <c r="U15" t="n">
-        <v>2.01</v>
+        <v>2.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '90+5']</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>['48', '53', '55', '84']</t>
+          <t>['19', '61']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN15" t="n">
         <v>3</v>
       </c>
-      <c r="AN15" t="n">
-        <v>8</v>
-      </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.87</v>
+        <v>1.07</v>
       </c>
       <c r="AS15" t="n">
         <v>38</v>
       </c>
       <c r="AT15" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46168.58333333334</v>
@@ -2909,41 +2909,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
         <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>['38', '43', '48']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>['53', '64', '73', '85']</t>
+          <t>['19', '41']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3033,25 +3033,25 @@
         <v>5</v>
       </c>
       <c r="AN16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.28</v>
+        <v>1.94</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="AS16" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="AT16" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46168.58333333334</v>
@@ -3068,41 +3068,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
         <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="U17" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.04</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['38', '43', '48']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>['19', '41']</t>
+          <t>['53', '64', '73', '85']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3192,25 +3192,25 @@
         <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="AS17" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="AT17" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46168.58333333334</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,139 +3237,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>['48', '53', '55', '84']</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>['15', '45+5', '82']</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>5</v>
-      </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AO18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.65</v>
+        <v>1.87</v>
       </c>
       <c r="AS18" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46168.58333333334</v>
